--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-25).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-08-25).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>19</t>
+    <t>17</t>
   </si>
   <si>
-    <t>R$ 4.914,25</t>
+    <t>R$ 4.891,46</t>
   </si>
   <si>
-    <t>50.8</t>
+    <t>50.6</t>
   </si>
   <si>
     <t>29.8</t>
   </si>
   <si>
-    <t>5.12</t>
+    <t>5.13</t>
   </si>
   <si>
-    <t>18.0</t>
+    <t>18.1</t>
   </si>
   <si>
-    <t>6.2</t>
+    <t>6.3</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>43.2%</t>
+    <t>43.4%</t>
   </si>
   <si>
     <t>17.3%</t>
@@ -6806,7 +6806,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6836,14 +6836,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>4294</v>
+      </c>
+      <c r="N36" s="6">
+        <v>44</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>6.4336812500000002</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>22.475521874999998</v>
+      </c>
+      <c r="R36" s="8">
+        <v>9.2489258064516129</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.34375</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9095,7 +9107,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9125,14 +9137,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1044.7</v>
+      </c>
+      <c r="N51" s="6">
+        <v>10</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>5.3650000000000002</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>32.241675000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>18.916675000000001</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.25</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
